--- a/note.xlsx
+++ b/note.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hskw1\Desktop\修理アプリファイル\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af69c26be6256a92/work/会社アプリ関連/チェア修理アプリ用/修理アプリファイル/githubアップロードセット/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC1C098-CE5E-431A-B8A3-5A3700E2D2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{0BC1C098-CE5E-431A-B8A3-5A3700E2D2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A7D55EA-E6F5-43B8-9077-EEB014BD801B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A1435EAF-3A90-4091-8BF9-535E8962D7EC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A1435EAF-3A90-4091-8BF9-535E8962D7EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
   <si>
     <t>　座面割れの部分接着及び現在割れていない部分も割れが生じないか叩き点検をします。</t>
     <rPh sb="1" eb="3">
@@ -77,46 +77,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　注）座面の裏に桟を取り付ける旨、事前にお伝えください。(若干重量が重くなる）</t>
-    <rPh sb="1" eb="2">
-      <t>チュウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ザメン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ウラ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>サン</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ムネ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ツタ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ジャッカン</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ジュウリョウ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>オモ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>　注）割れが多い場合は座面を交換させて頂くこともございます。</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -846,6 +806,53 @@
   </si>
   <si>
     <t>キャスター修理</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>座面再接着のみ１年保証（得意先にのみ説明）</t>
+    <rPh sb="8" eb="11">
+      <t>ネンホショウ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>トクイサキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　注）座面の裏に桟を取り付けは２０２６/2月末に終了。可温・接着・圧締・養生の見直しにより。</t>
+    <rPh sb="1" eb="2">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ザメン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウラ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>サン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>マツ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ミナオ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -853,7 +860,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1299,46 +1306,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F72A912-4B4F-474C-8EA8-F0058EB58B7A}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.83203125" customWidth="1"/>
-    <col min="3" max="3" width="71.58203125" customWidth="1"/>
-    <col min="4" max="4" width="52.75" customWidth="1"/>
-    <col min="5" max="5" width="37.33203125" customWidth="1"/>
-    <col min="6" max="6" width="63.25" customWidth="1"/>
-    <col min="7" max="7" width="71.75" customWidth="1"/>
+    <col min="1" max="1" width="35.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="71.59765625" customWidth="1"/>
+    <col min="4" max="4" width="52.69921875" customWidth="1"/>
+    <col min="5" max="5" width="88.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="63.19921875" customWidth="1"/>
+    <col min="7" max="7" width="71.69921875" customWidth="1"/>
+    <col min="8" max="8" width="80.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>49</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>0</v>
@@ -1350,203 +1358,205 @@
         <v>2</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>9</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>33</v>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A4" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>9</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>34</v>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="C6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -1556,15 +1566,15 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -1572,18 +1582,18 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -1593,36 +1603,36 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -1631,28 +1641,28 @@
       <c r="H15" s="10"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>29</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="18" spans="2:9">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -1661,7 +1671,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="2:9">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -1671,7 +1681,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="2:9">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -1680,9 +1690,9 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
-    <row r="22" spans="2:9">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/note.xlsx
+++ b/note.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af69c26be6256a92/work/会社アプリ関連/チェア修理アプリ用/修理アプリファイル/githubアップロードセット/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{0BC1C098-CE5E-431A-B8A3-5A3700E2D2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A7D55EA-E6F5-43B8-9077-EEB014BD801B}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{0BC1C098-CE5E-431A-B8A3-5A3700E2D2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32D39AAF-12D0-4296-BA07-AABAB378B545}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A1435EAF-3A90-4091-8BF9-535E8962D7EC}"/>
   </bookViews>
@@ -822,14 +822,14 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　注）座面の裏に桟を取り付けは２０２６/2月末に終了。可温・接着・圧締・養生の見直しにより。</t>
+    <t>　注）座面裏への桟の取り付けは２０２６/2月末に終了しまいた。可温・接着・圧締・養生の見直しにより。</t>
     <rPh sb="1" eb="2">
       <t>チュウ</t>
     </rPh>
     <rPh sb="3" eb="5">
       <t>ザメン</t>
     </rPh>
-    <rPh sb="6" eb="7">
+    <rPh sb="5" eb="6">
       <t>ウラ</t>
     </rPh>
     <rPh sb="8" eb="9">
@@ -850,7 +850,7 @@
     <rPh sb="24" eb="26">
       <t>シュウリョウ</t>
     </rPh>
-    <rPh sb="39" eb="41">
+    <rPh sb="43" eb="45">
       <t>ミナオ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -986,6 +986,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
